--- a/LISTADO DE REPUESTOS CRÍTICOS PLANTILLA.xlsx
+++ b/LISTADO DE REPUESTOS CRÍTICOS PLANTILLA.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccubias\Desktop\OneDrive_2025-05-22\Repuestos Criticos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{379E16A4-F397-4DF1-95FD-BF5447E8136D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA1E793-C1AF-48D8-A403-A5A0FAA93095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="R. C. ACAJUTLA" sheetId="29" r:id="rId1"/>
+    <sheet name="REPUESTOS" sheetId="29" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'R. C. ACAJUTLA'!$A$1:$P$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REPUESTOS!$A$1:$P$74</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
